--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/2330-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/2330-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5C68102F-A4FD-47F9-B02D-CC8039B4C810}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CCEB4AB5-D925-4346-B1B4-0F8F680F9EFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{92F5CD35-3159-4DBF-A6FF-DFD774F8883C}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{9C7C6317-A8B6-4286-89F4-67E8A062C2BE}"/>
   </bookViews>
   <sheets>
     <sheet name="2330-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1646,28 +1646,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D7F0B8E-1E9B-4BD9-B521-A7C79F9E27C8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{402D7366-A18B-485B-8960-F976AFE82997}">
   <dimension ref="A1:X69"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="7.125" customWidth="1"/>
-    <col min="5" max="5" width="6.75" customWidth="1"/>
-    <col min="6" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="15" width="7.125" customWidth="1"/>
-    <col min="16" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.375" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="4" width="6.109375" customWidth="1"/>
+    <col min="5" max="5" width="5.88671875" customWidth="1"/>
+    <col min="6" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="15" width="6.109375" customWidth="1"/>
+    <col min="16" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1701,7 +1701,7 @@
       <c r="W1" s="32"/>
       <c r="X1" s="24"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1737,7 +1737,7 @@
       <c r="W2" s="34"/>
       <c r="X2" s="35"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1789,7 +1789,7 @@
       </c>
       <c r="X3" s="38"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1857,7 +1857,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="39">
         <v>2025</v>
       </c>
@@ -1929,7 +1929,7 @@
         <v>2.06</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>28</v>
       </c>
@@ -2003,7 +2003,7 @@
         <v>0.39</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>28</v>
       </c>
@@ -2077,7 +2077,7 @@
         <v>0.39</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
         <v>28</v>
       </c>
@@ -2151,7 +2151,7 @@
         <v>0.64</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>28</v>
       </c>
@@ -2225,7 +2225,7 @@
         <v>0.64</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="41">
         <v>2024</v>
       </c>
@@ -2297,7 +2297,7 @@
         <v>2.5499999999999998</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="16" t="s">
         <v>28</v>
       </c>
@@ -2371,7 +2371,7 @@
         <v>0.57999999999999996</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="16" t="s">
         <v>28</v>
       </c>
@@ -2445,7 +2445,7 @@
         <v>0.57999999999999996</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="16" t="s">
         <v>28</v>
       </c>
@@ -2519,7 +2519,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="16" t="s">
         <v>28</v>
       </c>
@@ -2593,7 +2593,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="39">
         <v>2023</v>
       </c>
@@ -2665,7 +2665,7 @@
         <v>2.57</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="11" t="s">
         <v>28</v>
       </c>
@@ -2739,7 +2739,7 @@
         <v>0.61</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
         <v>28</v>
       </c>
@@ -2813,7 +2813,7 @@
         <v>0.61</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
         <v>28</v>
       </c>
@@ -2887,7 +2887,7 @@
         <v>0.68</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
         <v>28</v>
       </c>
@@ -2961,7 +2961,7 @@
         <v>0.68</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="41">
         <v>2022</v>
       </c>
@@ -3033,7 +3033,7 @@
         <v>2.73</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="16" t="s">
         <v>28</v>
       </c>
@@ -3107,7 +3107,7 @@
         <v>0.62</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="16" t="s">
         <v>28</v>
       </c>
@@ -3181,7 +3181,7 @@
         <v>0.62</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="16" t="s">
         <v>28</v>
       </c>
@@ -3255,7 +3255,7 @@
         <v>0.74</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="16" t="s">
         <v>28</v>
       </c>
@@ -3329,7 +3329,7 @@
         <v>0.74</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="39">
         <v>2021</v>
       </c>
@@ -3401,7 +3401,7 @@
         <v>2.5499999999999998</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="11" t="s">
         <v>28</v>
       </c>
@@ -3475,7 +3475,7 @@
         <v>0.74</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="11" t="s">
         <v>28</v>
       </c>
@@ -3549,7 +3549,7 @@
         <v>0.74</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="11" t="s">
         <v>28</v>
       </c>
@@ -3623,7 +3623,7 @@
         <v>0.53</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="11" t="s">
         <v>28</v>
       </c>
@@ -3697,7 +3697,7 @@
         <v>0.53</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="41">
         <v>2020</v>
       </c>
@@ -3769,7 +3769,7 @@
         <v>3.09</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="16" t="s">
         <v>28</v>
       </c>
@@ -3843,7 +3843,7 @@
         <v>0.48</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="16" t="s">
         <v>28</v>
       </c>
@@ -3917,7 +3917,7 @@
         <v>0.48</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="16" t="s">
         <v>28</v>
       </c>
@@ -3991,7 +3991,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="16" t="s">
         <v>28</v>
       </c>
@@ -4065,7 +4065,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="39">
         <v>2019</v>
       </c>
@@ -4137,7 +4137,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="11" t="s">
         <v>28</v>
       </c>
@@ -4211,7 +4211,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="11" t="s">
         <v>28</v>
       </c>
@@ -4285,7 +4285,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="11" t="s">
         <v>28</v>
       </c>
@@ -4359,7 +4359,7 @@
         <v>1.21</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="11" t="s">
         <v>28</v>
       </c>
@@ -4433,7 +4433,7 @@
         <v>0.97</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="41">
         <v>2018</v>
       </c>
@@ -4505,7 +4505,7 @@
         <v>3.87</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="39">
         <v>2017</v>
       </c>
@@ -4577,7 +4577,7 @@
         <v>3.81</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="41">
         <v>2016</v>
       </c>
@@ -4649,7 +4649,7 @@
         <v>3.91</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="39">
         <v>2015</v>
       </c>
@@ -4721,7 +4721,7 @@
         <v>4.5999999999999996</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="41">
         <v>2014</v>
       </c>
@@ -4793,7 +4793,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="39">
         <v>2013</v>
       </c>
@@ -4865,7 +4865,7 @@
         <v>2.98</v>
       </c>
     </row>
-    <row r="46" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="41">
         <v>2012</v>
       </c>
@@ -4937,7 +4937,7 @@
         <v>3.23</v>
       </c>
     </row>
-    <row r="47" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="39">
         <v>2011</v>
       </c>
@@ -5009,7 +5009,7 @@
         <v>4.0599999999999996</v>
       </c>
     </row>
-    <row r="48" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A48" s="41">
         <v>2010</v>
       </c>
@@ -5081,7 +5081,7 @@
         <v>4.82</v>
       </c>
     </row>
-    <row r="49" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A49" s="39">
         <v>2009</v>
       </c>
@@ -5153,7 +5153,7 @@
         <v>5.26</v>
       </c>
     </row>
-    <row r="50" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A50" s="41">
         <v>2008</v>
       </c>
@@ -5225,7 +5225,7 @@
         <v>7.88</v>
       </c>
     </row>
-    <row r="51" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A51" s="39">
         <v>2007</v>
       </c>
@@ -5297,7 +5297,7 @@
         <v>8.4499999999999993</v>
       </c>
     </row>
-    <row r="52" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A52" s="41">
         <v>2006</v>
       </c>
@@ -5369,7 +5369,7 @@
         <v>5.31</v>
       </c>
     </row>
-    <row r="53" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A53" s="39">
         <v>2005</v>
       </c>
@@ -5441,7 +5441,7 @@
         <v>5.35</v>
       </c>
     </row>
-    <row r="54" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A54" s="41">
         <v>2004</v>
       </c>
@@ -5513,7 +5513,7 @@
         <v>5.41</v>
       </c>
     </row>
-    <row r="55" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A55" s="39">
         <v>2003</v>
       </c>
@@ -5585,7 +5585,7 @@
         <v>4.9400000000000004</v>
       </c>
     </row>
-    <row r="56" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A56" s="41">
         <v>2002</v>
       </c>
@@ -5657,7 +5657,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A57" s="39">
         <v>2001</v>
       </c>
@@ -5729,7 +5729,7 @@
         <v>2.87</v>
       </c>
     </row>
-    <row r="58" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A58" s="41">
         <v>2000</v>
       </c>
@@ -5801,7 +5801,7 @@
         <v>9.17</v>
       </c>
     </row>
-    <row r="59" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A59" s="39">
         <v>1999</v>
       </c>
@@ -5873,7 +5873,7 @@
         <v>3.76</v>
       </c>
     </row>
-    <row r="60" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A60" s="41">
         <v>1998</v>
       </c>
@@ -5945,7 +5945,7 @@
         <v>3.38</v>
       </c>
     </row>
-    <row r="61" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A61" s="39">
         <v>1997</v>
       </c>
@@ -6017,7 +6017,7 @@
         <v>7.96</v>
       </c>
     </row>
-    <row r="62" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A62" s="41">
         <v>1996</v>
       </c>
@@ -6089,7 +6089,7 @@
         <v>9.01</v>
       </c>
     </row>
-    <row r="63" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A63" s="39">
         <v>1995</v>
       </c>
@@ -6161,7 +6161,7 @@
         <v>16.3</v>
       </c>
     </row>
-    <row r="64" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A64" s="41">
         <v>1994</v>
       </c>
@@ -6233,7 +6233,7 @@
         <v>10.4</v>
       </c>
     </row>
-    <row r="65" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A65" s="39">
         <v>1993</v>
       </c>
@@ -6305,7 +6305,7 @@
         <v>3.62</v>
       </c>
     </row>
-    <row r="66" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A66" s="41">
         <v>1992</v>
       </c>
@@ -6377,7 +6377,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="67" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A67" s="43">
         <v>1991</v>
       </c>
@@ -6449,7 +6449,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="68" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A68" s="45"/>
       <c r="B68" s="46"/>
       <c r="C68" s="22" t="s">
@@ -6477,7 +6477,7 @@
       <c r="W68" s="52"/>
       <c r="X68" s="48"/>
     </row>
-    <row r="69" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A69" s="41" t="s">
         <v>89</v>
       </c>
